--- a/Partial-Entries-Converted-to-Apps/06-29-26-enlight-partials-converted-to-apps-this-week.xlsx
+++ b/Partial-Entries-Converted-to-Apps/06-29-26-enlight-partials-converted-to-apps-this-week.xlsx
@@ -415,13 +415,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E12"/>
+  <dimension ref="A1:E19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20.9" customWidth="1" min="1" max="1"/>
-    <col width="18.7" customWidth="1" min="2" max="2"/>
-    <col width="27.5" customWidth="1" min="3" max="3"/>
-    <col width="39.6" customWidth="1" min="4" max="4"/>
+    <col width="19.8" customWidth="1" min="2" max="2"/>
+    <col width="22" customWidth="1" min="3" max="3"/>
+    <col width="37.40000000000001" customWidth="1" min="4" max="4"/>
     <col width="33" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
@@ -455,297 +455,486 @@
     <row r="2" ht="18" customHeight="1">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>003QP00001b0usQ</t>
+          <t>003QP00001c0dsc</t>
         </is>
       </c>
       <c r="B2" s="1" t="inlineStr">
         <is>
-          <t>FRANCIS</t>
+          <t>Claytos</t>
         </is>
       </c>
       <c r="C2" s="1" t="inlineStr">
         <is>
-          <t>BATEIREHO</t>
+          <t>Chimoto</t>
         </is>
       </c>
       <c r="D2" s="1" t="inlineStr">
         <is>
-          <t>bateireho@watotowasoka.ug</t>
+          <t>chimotoclaytos@gmail.com</t>
         </is>
       </c>
       <c r="E2" s="1" t="inlineStr">
         <is>
-          <t>06-15-2026</t>
+          <t>06-22-2026</t>
         </is>
       </c>
     </row>
     <row r="3" ht="18" customHeight="1">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>003QP00001b957X</t>
+          <t>003QP00001c1Oy0</t>
         </is>
       </c>
       <c r="B3" s="1" t="inlineStr">
         <is>
-          <t>stephen</t>
+          <t>Chinasa Lovlyn</t>
         </is>
       </c>
       <c r="C3" s="1" t="inlineStr">
         <is>
-          <t>revocatus</t>
+          <t>Nwachukwu</t>
         </is>
       </c>
       <c r="D3" s="1" t="inlineStr">
         <is>
-          <t>stephenrevocatus31@gmail.com</t>
+          <t>lovlyn122@gmail.com</t>
         </is>
       </c>
       <c r="E3" s="1" t="inlineStr">
         <is>
-          <t>06-16-2026</t>
+          <t>06-22-2026</t>
         </is>
       </c>
     </row>
     <row r="4" ht="18" customHeight="1">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>003QP00001bOKas</t>
+          <t>003QP00001c1eQ3</t>
         </is>
       </c>
       <c r="B4" s="1" t="inlineStr">
         <is>
-          <t>Bilal</t>
+          <t>Kla</t>
         </is>
       </c>
       <c r="C4" s="1" t="inlineStr">
         <is>
-          <t>Ahmed Ali</t>
+          <t>DOUABOU</t>
         </is>
       </c>
       <c r="D4" s="1" t="inlineStr">
         <is>
-          <t>psych.bilal@gmail.com</t>
+          <t>klakakouatman@gmail.com</t>
         </is>
       </c>
       <c r="E4" s="1" t="inlineStr">
         <is>
-          <t>06-17-2026</t>
+          <t>06-22-2026</t>
         </is>
       </c>
     </row>
     <row r="5" ht="18" customHeight="1">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>003QP00001bRCKE</t>
+          <t>0033h0000187BtJ</t>
         </is>
       </c>
       <c r="B5" s="1" t="inlineStr">
         <is>
-          <t>Ornella</t>
+          <t>Nelly</t>
         </is>
       </c>
       <c r="C5" s="1" t="inlineStr">
         <is>
-          <t>Hasimbola Dechen</t>
+          <t>Kininga</t>
         </is>
       </c>
       <c r="D5" s="1" t="inlineStr">
         <is>
-          <t>ornelladechenhasimbola@gmail.com</t>
+          <t>nellyhapp12@gmail.com</t>
         </is>
       </c>
       <c r="E5" s="1" t="inlineStr">
         <is>
-          <t>06-17-2026</t>
+          <t>06-23-2026</t>
         </is>
       </c>
     </row>
     <row r="6" ht="18" customHeight="1">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>003QP00001bVuWM</t>
+          <t>0033h00001LNbX3</t>
         </is>
       </c>
       <c r="B6" s="1" t="inlineStr">
         <is>
-          <t>ASIMA</t>
+          <t>SSEKABIRA</t>
         </is>
       </c>
       <c r="C6" s="1" t="inlineStr">
         <is>
-          <t>KAPALEPALE</t>
+          <t>NAJIB</t>
         </is>
       </c>
       <c r="D6" s="1" t="inlineStr">
         <is>
-          <t>kapalepaleasima@gmail.com</t>
+          <t>ssekabiranajib@gmail.com</t>
         </is>
       </c>
       <c r="E6" s="1" t="inlineStr">
         <is>
-          <t>06-18-2026</t>
+          <t>06-23-2026</t>
         </is>
       </c>
     </row>
     <row r="7" ht="18" customHeight="1">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>003QP00001bW3L7</t>
+          <t>003QP00001cHA1N</t>
         </is>
       </c>
       <c r="B7" s="1" t="inlineStr">
         <is>
-          <t>Yufei</t>
+          <t>RAYWIN OLOKWAO</t>
         </is>
       </c>
       <c r="C7" s="1" t="inlineStr">
         <is>
-          <t>Rao</t>
+          <t>ALUTA</t>
         </is>
       </c>
       <c r="D7" s="1" t="inlineStr">
         <is>
-          <t>picklephil180@gmail.com</t>
+          <t>raywinolokwaoaluta24@gmail.com</t>
         </is>
       </c>
       <c r="E7" s="1" t="inlineStr">
         <is>
-          <t>06-18-2026</t>
+          <t>06-23-2026</t>
         </is>
       </c>
     </row>
     <row r="8" ht="18" customHeight="1">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>003QP00001bYj6X</t>
+          <t>003QP00001c8Qmc</t>
         </is>
       </c>
       <c r="B8" s="1" t="inlineStr">
         <is>
-          <t>Ana Lua</t>
+          <t>Ng Adhi</t>
         </is>
       </c>
       <c r="C8" s="1" t="inlineStr">
         <is>
-          <t>Rodrigues Portes Good</t>
+          <t>Wahyudi</t>
         </is>
       </c>
       <c r="D8" s="1" t="inlineStr">
         <is>
-          <t>anaportes.apply@gmail.com</t>
+          <t>officialadhi@gmail.com</t>
         </is>
       </c>
       <c r="E8" s="1" t="inlineStr">
         <is>
-          <t>06-18-2026</t>
+          <t>06-23-2026</t>
         </is>
       </c>
     </row>
     <row r="9" ht="18" customHeight="1">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>003QP00001bYvZB</t>
+          <t>003QP00001cHsaH</t>
         </is>
       </c>
       <c r="B9" s="1" t="inlineStr">
         <is>
-          <t>Chenyao</t>
+          <t>Rita</t>
         </is>
       </c>
       <c r="C9" s="1" t="inlineStr">
         <is>
-          <t>Zhang</t>
+          <t>Adamik</t>
         </is>
       </c>
       <c r="D9" s="1" t="inlineStr">
         <is>
-          <t>chenyao.zhang0328@gmail.com</t>
+          <t>adamikritaa@gmail.com</t>
         </is>
       </c>
       <c r="E9" s="1" t="inlineStr">
         <is>
-          <t>06-18-2026</t>
+          <t>06-24-2026</t>
         </is>
       </c>
     </row>
     <row r="10" ht="18" customHeight="1">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>003QP00001bfkYx</t>
+          <t>003QP00001cZHxF</t>
         </is>
       </c>
       <c r="B10" s="1" t="inlineStr">
         <is>
-          <t>Tigist</t>
+          <t>Flora</t>
         </is>
       </c>
       <c r="C10" s="1" t="inlineStr">
         <is>
-          <t>Kassa</t>
+          <t>Mwang'onda</t>
         </is>
       </c>
       <c r="D10" s="1" t="inlineStr">
         <is>
-          <t>tgafro21@gmail.com</t>
+          <t>lolasewa@gmail.com</t>
         </is>
       </c>
       <c r="E10" s="1" t="inlineStr">
         <is>
-          <t>06-19-2026</t>
+          <t>06-25-2026</t>
         </is>
       </c>
     </row>
     <row r="11" ht="18" customHeight="1">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>003QP00001bkjlt</t>
+          <t>003QP00001ccV7n</t>
         </is>
       </c>
       <c r="B11" s="1" t="inlineStr">
         <is>
-          <t>Rhode Bermine</t>
+          <t>Srishti</t>
         </is>
       </c>
       <c r="C11" s="1" t="inlineStr">
         <is>
-          <t>Banatte</t>
+          <t>Srivastava</t>
         </is>
       </c>
       <c r="D11" s="1" t="inlineStr">
         <is>
-          <t>bbanatte@gmail.com</t>
+          <t>ceo@infiheal.com</t>
         </is>
       </c>
       <c r="E11" s="1" t="inlineStr">
         <is>
-          <t>06-19-2026</t>
+          <t>06-26-2026</t>
         </is>
       </c>
     </row>
     <row r="12" ht="18" customHeight="1">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>003QP00001bpq3g</t>
+          <t>003QP00001ccFEE</t>
         </is>
       </c>
       <c r="B12" s="1" t="inlineStr">
         <is>
-          <t>André</t>
+          <t>Fathur</t>
         </is>
       </c>
       <c r="C12" s="1" t="inlineStr">
         <is>
-          <t>Smith</t>
+          <t>ozi</t>
         </is>
       </c>
       <c r="D12" s="1" t="inlineStr">
         <is>
-          <t>smithandre10@gmail.com</t>
+          <t>fathurozi862@gmail.com</t>
         </is>
       </c>
       <c r="E12" s="1" t="inlineStr">
         <is>
-          <t>06-20-2026</t>
+          <t>06-26-2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="18" customHeight="1">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>003QP00001cjm3p</t>
+        </is>
+      </c>
+      <c r="B13" s="1" t="inlineStr">
+        <is>
+          <t>Tarlisha</t>
+        </is>
+      </c>
+      <c r="C13" s="1" t="inlineStr">
+        <is>
+          <t>Cooper</t>
+        </is>
+      </c>
+      <c r="D13" s="1" t="inlineStr">
+        <is>
+          <t>ctarlisha@yahoo.com</t>
+        </is>
+      </c>
+      <c r="E13" s="1" t="inlineStr">
+        <is>
+          <t>06-26-2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="18" customHeight="1">
+      <c r="A14" s="1" t="inlineStr">
+        <is>
+          <t>003QP00001b7qc4</t>
+        </is>
+      </c>
+      <c r="B14" s="1" t="inlineStr">
+        <is>
+          <t>POONAM</t>
+        </is>
+      </c>
+      <c r="C14" s="1" t="inlineStr">
+        <is>
+          <t>MAHRAJ</t>
+        </is>
+      </c>
+      <c r="D14" s="1" t="inlineStr">
+        <is>
+          <t>dr.poonammahraj.pt@gmail.com</t>
+        </is>
+      </c>
+      <c r="E14" s="1" t="inlineStr">
+        <is>
+          <t>06-27-2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="18" customHeight="1">
+      <c r="A15" s="1" t="inlineStr">
+        <is>
+          <t>003QP00001cmRXN</t>
+        </is>
+      </c>
+      <c r="B15" s="1" t="inlineStr">
+        <is>
+          <t>Anupama</t>
+        </is>
+      </c>
+      <c r="C15" s="1" t="inlineStr">
+        <is>
+          <t>Mishra</t>
+        </is>
+      </c>
+      <c r="D15" s="1" t="inlineStr">
+        <is>
+          <t>anumiahra483892@gmail.com</t>
+        </is>
+      </c>
+      <c r="E15" s="1" t="inlineStr">
+        <is>
+          <t>06-27-2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="18" customHeight="1">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>003QP00001cwUYx</t>
+        </is>
+      </c>
+      <c r="B16" s="1" t="inlineStr">
+        <is>
+          <t>saphira</t>
+        </is>
+      </c>
+      <c r="C16" s="1" t="inlineStr">
+        <is>
+          <t>munthali-mulemba</t>
+        </is>
+      </c>
+      <c r="D16" s="1" t="inlineStr">
+        <is>
+          <t>saphira.mulemba@gmail.com</t>
+        </is>
+      </c>
+      <c r="E16" s="1" t="inlineStr">
+        <is>
+          <t>06-29-2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="18" customHeight="1">
+      <c r="A17" s="1" t="inlineStr">
+        <is>
+          <t>003QP00001cxtDN</t>
+        </is>
+      </c>
+      <c r="B17" s="1" t="inlineStr">
+        <is>
+          <t>Cecilia</t>
+        </is>
+      </c>
+      <c r="C17" s="1" t="inlineStr">
+        <is>
+          <t>Dadi</t>
+        </is>
+      </c>
+      <c r="D17" s="1" t="inlineStr">
+        <is>
+          <t>cdadi@wilcah.org</t>
+        </is>
+      </c>
+      <c r="E17" s="1" t="inlineStr">
+        <is>
+          <t>06-29-2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="18" customHeight="1">
+      <c r="A18" s="1" t="inlineStr">
+        <is>
+          <t>003QP00001czXiD</t>
+        </is>
+      </c>
+      <c r="B18" s="1" t="inlineStr">
+        <is>
+          <t>Marion</t>
+        </is>
+      </c>
+      <c r="C18" s="1" t="inlineStr">
+        <is>
+          <t>Yego</t>
+        </is>
+      </c>
+      <c r="D18" s="1" t="inlineStr">
+        <is>
+          <t>yegomarion@artnovax.org</t>
+        </is>
+      </c>
+      <c r="E18" s="1" t="inlineStr">
+        <is>
+          <t>06-29-2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="18" customHeight="1">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>003QP00001cvtMM</t>
+        </is>
+      </c>
+      <c r="B19" s="1" t="inlineStr">
+        <is>
+          <t>Peris</t>
+        </is>
+      </c>
+      <c r="C19" s="1" t="inlineStr">
+        <is>
+          <t>Mutena</t>
+        </is>
+      </c>
+      <c r="D19" s="1" t="inlineStr">
+        <is>
+          <t>teshperis8@gmail.com</t>
+        </is>
+      </c>
+      <c r="E19" s="1" t="inlineStr">
+        <is>
+          <t>06-29-2026</t>
         </is>
       </c>
     </row>
